--- a/public/調査報告書様式.xlsx
+++ b/public/調査報告書様式.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lab\NodeCloud\NodeCloudICT\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C65EAED-B8AC-4021-A6CB-23AFCACFE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30D4EFA-507C-4562-A12B-E432FC12E818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{45AFC3DD-1542-44B8-8D5B-99EAED8AAD96}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="153">
   <si>
     <t>不動産登記規則第93条ただし書</t>
   </si>
@@ -595,16 +595,21 @@
   </si>
   <si>
     <t>{{P.CHANGE}}変更
-{{P.CORR}}更正
-{{P.CORR}}</t>
+{{P.CORR}}更正</t>
     <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>{{ANCHOR:OWNERS:START}}</t>
+  </si>
+  <si>
+    <t>{{ANCHOR:OWNERS:END}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -791,6 +796,19 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1607,7 +1625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="389">
+  <cellXfs count="391">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2770,6 +2788,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4129,6 +4153,9 @@
       <c r="AM20" s="168"/>
       <c r="AN20" s="168"/>
       <c r="AO20" s="169"/>
+      <c r="AP20" s="390" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="21" spans="1:58" ht="19.5" customHeight="1">
       <c r="A21" s="42"/>
@@ -4178,6 +4205,7 @@
       <c r="AM21" s="98"/>
       <c r="AN21" s="98"/>
       <c r="AO21" s="163"/>
+      <c r="AP21" s="390"/>
     </row>
     <row r="22" spans="1:58" ht="19.5" customHeight="1">
       <c r="A22" s="42"/>
@@ -4691,6 +4719,9 @@
       <c r="AM32" s="219"/>
       <c r="AN32" s="219"/>
       <c r="AO32" s="220"/>
+      <c r="AP32" s="389" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="33" spans="1:58" ht="15" customHeight="1" thickBot="1">
       <c r="A33" s="56"/>

--- a/public/調査報告書様式.xlsx
+++ b/public/調査報告書様式.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lab\NodeCloud\NodeCloudICT\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE6AA85-95B5-421B-8C4E-BEA7ECB9DA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F5DC0A-C277-41BE-BF38-E7F83278D0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{45AFC3DD-1542-44B8-8D5B-99EAED8AAD96}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="216">
   <si>
     <t>不動産登記規則第93条ただし書</t>
   </si>
@@ -321,10 +321,6 @@
   </si>
   <si>
     <t>地積更正の要否</t>
-  </si>
-  <si>
-    <t>□要　□否</t>
-    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>10　補足・特記事項</t>
@@ -736,18 +732,11 @@
     <t>　{{MTH_STATIC}}スタティック　　{{MTH_SHORT_STATIC}}短縮スタティック　　{{MTH_RTK}}RTK　　{{MTH_NET_RTK}}ネットワーク型RTK　{{MTH_GNSS_OTHER}}その他({{MTH_GNSS_OTHER_TEXT}})</t>
   </si>
   <si>
-    <t>{{PHOTO1_DATE}}</t>
-  </si>
-  <si>
     <t>{{PHOTO1_REMARK}}</t>
   </si>
   <si>
     <t>{{BP.GRADE}}</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{SG.DEV_TS}}トータルステーション　{{SG.DEV_GNSS}}GNSS　{{SG.DEV_OTHER}}その他（{{SG.DEV_OTHER_TEXT}}）</t>
-    <phoneticPr fontId="10"/>
   </si>
   <si>
     <t>{{SG.OBS_START}}～{{SG.OBS_END}}</t>
@@ -768,10 +757,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>{{ANCHOR:PHOTOS}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t xml:space="preserve">{{ANCHOR:BASE_POINTS}}  </t>
     <phoneticPr fontId="2"/>
   </si>
@@ -781,6 +766,70 @@
   </si>
   <si>
     <t xml:space="preserve">{{ANCHOR:PERM_FEATURES}} </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{SG.DEV_TS}}TS　{{SG.DEV_GNSS}}GNSS　{{SG.DEV_OTHER}}その他（{{SG.DEV_OTHER_TEXT}}）</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>{{K.LOCATION}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{K.NUMBER}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{K.DIFF}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{K.TOLERANCE}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{ANCHOR:KOOSA}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	{{K.MEASURED}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	{{K.NEEDS_CORR_YES}}要　{{K.NEEDS_CORR_NO}}否</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>{{ANCHOR:PHOTOS:START}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{ANCHOR:PHOTOS:END}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{PHOTO_IMG_1}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{PHOTO_IMG_2}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{PHOTO_DATE_1}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{PHOTO_DATE_2}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{{PHOTO_CAP_1}} </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{PHOTO_CAP_2}}</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3508,7 +3557,7 @@
       <c r="AN1" s="78"/>
       <c r="AO1" s="79"/>
       <c r="AP1" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:58" s="1" customFormat="1" ht="15" customHeight="1">
@@ -3615,7 +3664,7 @@
     <row r="5" spans="1:58" s="1" customFormat="1" ht="17.25" customHeight="1">
       <c r="B5" s="6"/>
       <c r="C5" s="43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q5" s="40"/>
       <c r="S5" s="40"/>
@@ -3633,7 +3682,7 @@
       <c r="T6" s="40"/>
       <c r="Y6" s="40"/>
       <c r="Z6" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
@@ -3655,7 +3704,7 @@
     <row r="7" spans="1:58" s="1" customFormat="1" ht="12">
       <c r="B7" s="6"/>
       <c r="C7" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q7" s="40"/>
       <c r="S7" s="40"/>
@@ -3679,7 +3728,7 @@
     <row r="8" spans="1:58" s="1" customFormat="1" ht="12">
       <c r="B8" s="6"/>
       <c r="C8" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -3738,7 +3787,7 @@
       <c r="V9" s="46"/>
       <c r="W9" s="46"/>
       <c r="X9" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y9" s="46"/>
       <c r="AA9" s="46"/>
@@ -3763,7 +3812,7 @@
     <row r="10" spans="1:58" s="1" customFormat="1" ht="12">
       <c r="B10" s="16"/>
       <c r="C10" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
@@ -3849,7 +3898,7 @@
     <row r="12" spans="1:58" ht="15" customHeight="1" thickBot="1">
       <c r="A12" s="55"/>
       <c r="B12" s="57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
@@ -3958,13 +4007,13 @@
     <row r="14" spans="1:58" s="12" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A14" s="56"/>
       <c r="B14" s="66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="67"/>
       <c r="E14" s="68"/>
       <c r="F14" s="69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
@@ -3998,13 +4047,13 @@
       <c r="AJ14" s="70"/>
       <c r="AK14" s="71"/>
       <c r="AL14" s="72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AM14" s="73"/>
       <c r="AN14" s="73"/>
       <c r="AO14" s="74"/>
       <c r="AP14" s="52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AQ14" s="21"/>
       <c r="AR14" s="21"/>
@@ -4207,13 +4256,13 @@
     <row r="18" spans="1:58" ht="27.65" customHeight="1" thickBot="1">
       <c r="A18" s="104"/>
       <c r="B18" s="93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="94"/>
       <c r="D18" s="94"/>
       <c r="E18" s="95"/>
       <c r="F18" s="96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G18" s="97"/>
       <c r="H18" s="97"/>
@@ -4227,43 +4276,43 @@
       <c r="P18" s="97"/>
       <c r="Q18" s="98"/>
       <c r="R18" s="89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S18" s="90"/>
       <c r="T18" s="90"/>
       <c r="U18" s="99"/>
       <c r="V18" s="100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W18" s="94"/>
       <c r="X18" s="94"/>
       <c r="Y18" s="95"/>
       <c r="Z18" s="101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="102"/>
       <c r="AB18" s="103"/>
       <c r="AC18" s="19"/>
       <c r="AD18" s="360" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AE18" s="361"/>
       <c r="AF18" s="361"/>
       <c r="AG18" s="362"/>
       <c r="AH18" s="89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AI18" s="90"/>
       <c r="AJ18" s="90"/>
       <c r="AK18" s="90"/>
       <c r="AL18" s="360" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AM18" s="361"/>
       <c r="AN18" s="361"/>
       <c r="AO18" s="363"/>
       <c r="AP18" s="51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:58" ht="19.5" customHeight="1" thickBot="1">
@@ -4320,7 +4369,7 @@
       <c r="D20" s="164"/>
       <c r="E20" s="165"/>
       <c r="F20" s="166" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G20" s="167"/>
       <c r="H20" s="167"/>
@@ -4358,13 +4407,13 @@
       <c r="AN20" s="167"/>
       <c r="AO20" s="168"/>
       <c r="AP20" s="52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:58" ht="19.5" customHeight="1">
       <c r="A21" s="37"/>
       <c r="B21" s="169" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170"/>
@@ -4379,7 +4428,7 @@
       <c r="K21" s="179"/>
       <c r="L21" s="180"/>
       <c r="M21" s="96" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N21" s="97"/>
       <c r="O21" s="97"/>
@@ -4427,7 +4476,7 @@
       <c r="K22" s="182"/>
       <c r="L22" s="183"/>
       <c r="M22" s="147" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N22" s="148"/>
       <c r="O22" s="148"/>
@@ -4474,7 +4523,7 @@
       <c r="K23" s="145"/>
       <c r="L23" s="146"/>
       <c r="M23" s="147" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N23" s="148"/>
       <c r="O23" s="148"/>
@@ -4521,7 +4570,7 @@
       <c r="K24" s="145"/>
       <c r="L24" s="146"/>
       <c r="M24" s="147" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N24" s="148"/>
       <c r="O24" s="148"/>
@@ -4568,7 +4617,7 @@
       <c r="K25" s="151"/>
       <c r="L25" s="152"/>
       <c r="M25" s="153" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N25" s="154"/>
       <c r="O25" s="154"/>
@@ -4606,7 +4655,7 @@
       <c r="D26" s="173"/>
       <c r="E26" s="174"/>
       <c r="F26" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G26" s="157"/>
       <c r="H26" s="157"/>
@@ -4660,7 +4709,7 @@
       <c r="K27" s="160"/>
       <c r="L27" s="161"/>
       <c r="M27" s="96" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N27" s="97"/>
       <c r="O27" s="97"/>
@@ -4707,7 +4756,7 @@
       <c r="K28" s="182"/>
       <c r="L28" s="183"/>
       <c r="M28" s="147" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N28" s="148"/>
       <c r="O28" s="148"/>
@@ -4754,7 +4803,7 @@
       <c r="K29" s="145"/>
       <c r="L29" s="146"/>
       <c r="M29" s="147" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N29" s="148"/>
       <c r="O29" s="148"/>
@@ -4801,7 +4850,7 @@
       <c r="K30" s="191"/>
       <c r="L30" s="192"/>
       <c r="M30" s="147" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N30" s="148"/>
       <c r="O30" s="148"/>
@@ -4848,7 +4897,7 @@
       <c r="K31" s="212"/>
       <c r="L31" s="213"/>
       <c r="M31" s="147" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N31" s="148"/>
       <c r="O31" s="148"/>
@@ -4893,7 +4942,7 @@
       <c r="K32" s="215"/>
       <c r="L32" s="216"/>
       <c r="M32" s="217" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N32" s="218"/>
       <c r="O32" s="218"/>
@@ -4924,7 +4973,7 @@
       <c r="AN32" s="218"/>
       <c r="AO32" s="219"/>
       <c r="AP32" s="54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:58" ht="15" customHeight="1" thickBot="1">
@@ -5028,18 +5077,18 @@
     <row r="35" spans="1:58" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="104"/>
       <c r="B35" s="196" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C35" s="197"/>
       <c r="D35" s="198"/>
       <c r="E35" s="199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F35" s="200"/>
       <c r="G35" s="200"/>
       <c r="H35" s="201"/>
       <c r="I35" s="202" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J35" s="203"/>
       <c r="K35" s="203"/>
@@ -5047,7 +5096,7 @@
       <c r="M35" s="203"/>
       <c r="N35" s="204"/>
       <c r="O35" s="205" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P35" s="206"/>
       <c r="Q35" s="206"/>
@@ -5056,7 +5105,7 @@
       <c r="T35" s="206"/>
       <c r="U35" s="207"/>
       <c r="V35" s="208" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="W35" s="209"/>
       <c r="X35" s="209"/>
@@ -5078,7 +5127,7 @@
       <c r="AN35" s="209"/>
       <c r="AO35" s="210"/>
       <c r="AP35" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:58" ht="15" customHeight="1" thickBot="1">
@@ -5221,7 +5270,7 @@
       <c r="I38" s="231"/>
       <c r="J38" s="232"/>
       <c r="K38" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L38" s="233" t="s">
         <v>33</v>
@@ -5269,7 +5318,7 @@
       <c r="I39" s="236"/>
       <c r="J39" s="237"/>
       <c r="K39" s="33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L39" s="238" t="s">
         <v>34</v>
@@ -5317,7 +5366,7 @@
       <c r="I40" s="236"/>
       <c r="J40" s="237"/>
       <c r="K40" s="33" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L40" s="238" t="s">
         <v>35</v>
@@ -5365,7 +5414,7 @@
       <c r="I41" s="236"/>
       <c r="J41" s="237"/>
       <c r="K41" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L41" s="238" t="s">
         <v>36</v>
@@ -5413,7 +5462,7 @@
       <c r="I42" s="236"/>
       <c r="J42" s="237"/>
       <c r="K42" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L42" s="238" t="s">
         <v>37</v>
@@ -5461,7 +5510,7 @@
       <c r="I43" s="236"/>
       <c r="J43" s="237"/>
       <c r="K43" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L43" s="238" t="s">
         <v>38</v>
@@ -5509,7 +5558,7 @@
       <c r="I44" s="236"/>
       <c r="J44" s="237"/>
       <c r="K44" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L44" s="238" t="s">
         <v>39</v>
@@ -5557,7 +5606,7 @@
       <c r="I45" s="236"/>
       <c r="J45" s="237"/>
       <c r="K45" s="33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L45" s="238" t="s">
         <v>40</v>
@@ -5605,7 +5654,7 @@
       <c r="I46" s="236"/>
       <c r="J46" s="237"/>
       <c r="K46" s="33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L46" s="238" t="s">
         <v>41</v>
@@ -5653,7 +5702,7 @@
       <c r="I47" s="236"/>
       <c r="J47" s="237"/>
       <c r="K47" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L47" s="238" t="s">
         <v>42</v>
@@ -5701,7 +5750,7 @@
       <c r="I48" s="236"/>
       <c r="J48" s="237"/>
       <c r="K48" s="33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L48" s="238" t="s">
         <v>43</v>
@@ -5749,7 +5798,7 @@
       <c r="I49" s="236"/>
       <c r="J49" s="237"/>
       <c r="K49" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L49" s="238" t="s">
         <v>44</v>
@@ -5797,7 +5846,7 @@
       <c r="I50" s="236"/>
       <c r="J50" s="237"/>
       <c r="K50" s="33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L50" s="238" t="s">
         <v>45</v>
@@ -5845,7 +5894,7 @@
       <c r="I51" s="241"/>
       <c r="J51" s="242"/>
       <c r="K51" s="35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L51" s="243" t="s">
         <v>45</v>
@@ -5895,7 +5944,7 @@
       <c r="I52" s="90"/>
       <c r="J52" s="99"/>
       <c r="K52" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L52" s="233" t="s">
         <v>47</v>
@@ -5943,7 +5992,7 @@
       <c r="I53" s="236"/>
       <c r="J53" s="237"/>
       <c r="K53" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L53" s="238" t="s">
         <v>48</v>
@@ -5991,7 +6040,7 @@
       <c r="I54" s="236"/>
       <c r="J54" s="237"/>
       <c r="K54" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L54" s="238" t="s">
         <v>49</v>
@@ -6039,7 +6088,7 @@
       <c r="I55" s="236"/>
       <c r="J55" s="237"/>
       <c r="K55" s="33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L55" s="238" t="s">
         <v>50</v>
@@ -6087,7 +6136,7 @@
       <c r="I56" s="236"/>
       <c r="J56" s="237"/>
       <c r="K56" s="33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L56" s="238" t="s">
         <v>51</v>
@@ -6135,7 +6184,7 @@
       <c r="I57" s="236"/>
       <c r="J57" s="237"/>
       <c r="K57" s="33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L57" s="238" t="s">
         <v>52</v>
@@ -6183,7 +6232,7 @@
       <c r="I58" s="236"/>
       <c r="J58" s="237"/>
       <c r="K58" s="33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L58" s="238" t="s">
         <v>53</v>
@@ -6231,7 +6280,7 @@
       <c r="I59" s="236"/>
       <c r="J59" s="237"/>
       <c r="K59" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L59" s="238" t="s">
         <v>54</v>
@@ -6279,7 +6328,7 @@
       <c r="I60" s="236"/>
       <c r="J60" s="237"/>
       <c r="K60" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L60" s="238" t="s">
         <v>55</v>
@@ -6327,7 +6376,7 @@
       <c r="I61" s="236"/>
       <c r="J61" s="237"/>
       <c r="K61" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L61" s="238" t="s">
         <v>56</v>
@@ -6375,7 +6424,7 @@
       <c r="I62" s="236"/>
       <c r="J62" s="237"/>
       <c r="K62" s="33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L62" s="238" t="s">
         <v>57</v>
@@ -6423,7 +6472,7 @@
       <c r="I63" s="236"/>
       <c r="J63" s="237"/>
       <c r="K63" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L63" s="238" t="s">
         <v>58</v>
@@ -6471,7 +6520,7 @@
       <c r="I64" s="236"/>
       <c r="J64" s="237"/>
       <c r="K64" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L64" s="238" t="s">
         <v>59</v>
@@ -6519,7 +6568,7 @@
       <c r="I65" s="236"/>
       <c r="J65" s="237"/>
       <c r="K65" s="33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L65" s="238" t="s">
         <v>44</v>
@@ -6567,7 +6616,7 @@
       <c r="I66" s="236"/>
       <c r="J66" s="237"/>
       <c r="K66" s="33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L66" s="238" t="s">
         <v>45</v>
@@ -6615,7 +6664,7 @@
       <c r="I67" s="257"/>
       <c r="J67" s="258"/>
       <c r="K67" s="22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L67" s="259" t="s">
         <v>45</v>
@@ -6665,7 +6714,7 @@
       <c r="I68" s="265"/>
       <c r="J68" s="266"/>
       <c r="K68" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L68" s="267" t="s">
         <v>61</v>
@@ -6713,7 +6762,7 @@
       <c r="I69" s="236"/>
       <c r="J69" s="237"/>
       <c r="K69" s="33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L69" s="238" t="s">
         <v>62</v>
@@ -6761,7 +6810,7 @@
       <c r="I70" s="236"/>
       <c r="J70" s="237"/>
       <c r="K70" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L70" s="238" t="s">
         <v>63</v>
@@ -6809,7 +6858,7 @@
       <c r="I71" s="236"/>
       <c r="J71" s="237"/>
       <c r="K71" s="33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L71" s="238" t="s">
         <v>64</v>
@@ -6857,7 +6906,7 @@
       <c r="I72" s="236"/>
       <c r="J72" s="237"/>
       <c r="K72" s="33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L72" s="238" t="s">
         <v>65</v>
@@ -6905,10 +6954,10 @@
       <c r="I73" s="236"/>
       <c r="J73" s="237"/>
       <c r="K73" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L73" s="238" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M73" s="238"/>
       <c r="N73" s="238"/>
@@ -6969,7 +7018,7 @@
       <c r="I74" s="236"/>
       <c r="J74" s="237"/>
       <c r="K74" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L74" s="238" t="s">
         <v>45</v>
@@ -7091,7 +7140,7 @@
       <c r="D76" s="274"/>
       <c r="E76" s="275"/>
       <c r="F76" s="276" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G76" s="276"/>
       <c r="H76" s="276"/>
@@ -7194,7 +7243,7 @@
     </row>
     <row r="78" spans="1:58" ht="15" customHeight="1" thickBot="1">
       <c r="B78" s="105" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C78" s="106"/>
       <c r="D78" s="106"/>
@@ -7246,7 +7295,7 @@
       <c r="F79" s="121"/>
       <c r="G79" s="122"/>
       <c r="H79" s="280" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I79" s="281"/>
       <c r="J79" s="281"/>
@@ -7292,7 +7341,7 @@
       <c r="F80" s="271"/>
       <c r="G80" s="272"/>
       <c r="H80" s="283" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I80" s="206"/>
       <c r="J80" s="206"/>
@@ -7426,7 +7475,7 @@
       <c r="F83" s="286"/>
       <c r="G83" s="286"/>
       <c r="H83" s="305" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I83" s="306"/>
       <c r="J83" s="306"/>
@@ -7472,7 +7521,7 @@
       <c r="F84" s="286"/>
       <c r="G84" s="286"/>
       <c r="H84" s="287" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I84" s="288"/>
       <c r="J84" s="288"/>
@@ -7519,7 +7568,7 @@
       <c r="F85" s="291"/>
       <c r="G85" s="291"/>
       <c r="H85" s="293" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I85" s="294"/>
       <c r="J85" s="294"/>
@@ -7564,7 +7613,7 @@
       <c r="F86" s="291"/>
       <c r="G86" s="291"/>
       <c r="H86" s="296" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I86" s="297"/>
       <c r="J86" s="297"/>
@@ -7610,7 +7659,7 @@
       <c r="F87" s="312"/>
       <c r="G87" s="312"/>
       <c r="H87" s="317" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I87" s="318"/>
       <c r="J87" s="318"/>
@@ -7706,7 +7755,7 @@
       <c r="F89" s="314"/>
       <c r="G89" s="314"/>
       <c r="H89" s="100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I89" s="94"/>
       <c r="J89" s="94"/>
@@ -7716,7 +7765,7 @@
       <c r="N89" s="94"/>
       <c r="O89" s="95"/>
       <c r="P89" s="89" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Q89" s="90"/>
       <c r="R89" s="90"/>
@@ -7730,7 +7779,7 @@
       <c r="Z89" s="90"/>
       <c r="AA89" s="99"/>
       <c r="AB89" s="89" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC89" s="90"/>
       <c r="AD89" s="90"/>
@@ -7746,7 +7795,7 @@
       <c r="AN89" s="90"/>
       <c r="AO89" s="311"/>
       <c r="AP89" s="51" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:42" ht="17.149999999999999" customHeight="1">
@@ -7809,7 +7858,7 @@
       <c r="F91" s="323"/>
       <c r="G91" s="323"/>
       <c r="H91" s="256" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I91" s="331"/>
       <c r="J91" s="331"/>
@@ -7819,7 +7868,7 @@
       <c r="N91" s="331"/>
       <c r="O91" s="332"/>
       <c r="P91" s="256" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q91" s="257"/>
       <c r="R91" s="257"/>
@@ -7833,7 +7882,7 @@
       <c r="Z91" s="257"/>
       <c r="AA91" s="257"/>
       <c r="AB91" s="256" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AC91" s="257"/>
       <c r="AD91" s="257"/>
@@ -7849,7 +7898,7 @@
       <c r="AN91" s="257"/>
       <c r="AO91" s="333"/>
       <c r="AP91" s="51" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:42" ht="17.149999999999999" customHeight="1">
@@ -7912,7 +7961,7 @@
       <c r="F93" s="323"/>
       <c r="G93" s="323"/>
       <c r="H93" s="330" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I93" s="331"/>
       <c r="J93" s="331"/>
@@ -7922,7 +7971,7 @@
       <c r="N93" s="331"/>
       <c r="O93" s="332"/>
       <c r="P93" s="256" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q93" s="257"/>
       <c r="R93" s="257"/>
@@ -7936,7 +7985,7 @@
       <c r="Z93" s="257"/>
       <c r="AA93" s="258"/>
       <c r="AB93" s="256" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC93" s="257"/>
       <c r="AD93" s="257"/>
@@ -7952,15 +8001,17 @@
       <c r="AN93" s="257"/>
       <c r="AO93" s="333"/>
       <c r="AP93" s="51" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:42" ht="153" customHeight="1">
       <c r="A94" s="55"/>
-      <c r="B94" s="337"/>
+      <c r="B94" s="337" t="s">
+        <v>214</v>
+      </c>
       <c r="C94" s="338"/>
       <c r="D94" s="353" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E94" s="354"/>
       <c r="F94" s="354"/>
@@ -7979,9 +8030,13 @@
       <c r="S94" s="354"/>
       <c r="T94" s="354"/>
       <c r="U94" s="355"/>
-      <c r="V94" s="343"/>
+      <c r="V94" s="343" t="s">
+        <v>215</v>
+      </c>
       <c r="W94" s="338"/>
-      <c r="X94" s="353"/>
+      <c r="X94" s="353" t="s">
+        <v>211</v>
+      </c>
       <c r="Y94" s="354"/>
       <c r="Z94" s="354"/>
       <c r="AA94" s="354"/>
@@ -7999,6 +8054,9 @@
       <c r="AM94" s="354"/>
       <c r="AN94" s="354"/>
       <c r="AO94" s="356"/>
+      <c r="AP94" s="51" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="95" spans="1:42" ht="17.149999999999999" customHeight="1">
       <c r="A95" s="104"/>
@@ -8008,7 +8066,7 @@
         <v>85</v>
       </c>
       <c r="J95" s="346" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="K95" s="347"/>
       <c r="L95" s="347"/>
@@ -8026,7 +8084,9 @@
       <c r="Y95" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="AD95" s="346"/>
+      <c r="AD95" s="346" t="s">
+        <v>213</v>
+      </c>
       <c r="AE95" s="347"/>
       <c r="AF95" s="347"/>
       <c r="AG95" s="347"/>
@@ -8052,7 +8112,7 @@
       <c r="H96" s="27"/>
       <c r="I96" s="27"/>
       <c r="J96" s="349" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K96" s="350"/>
       <c r="L96" s="350"/>
@@ -8087,10 +8147,13 @@
       <c r="AM96" s="350"/>
       <c r="AN96" s="350"/>
       <c r="AO96" s="352"/>
-    </row>
-    <row r="97" spans="1:41" ht="40.5" customHeight="1">
+      <c r="AP96" s="51" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="97" spans="1:42" ht="40.5" customHeight="1">
       <c r="B97" s="383" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C97" s="384"/>
       <c r="D97" s="384"/>
@@ -8132,7 +8195,7 @@
       <c r="AN97" s="387"/>
       <c r="AO97" s="388"/>
     </row>
-    <row r="98" spans="1:41" ht="17.149999999999999" customHeight="1">
+    <row r="98" spans="1:42" ht="17.149999999999999" customHeight="1">
       <c r="B98" s="302" t="s">
         <v>87</v>
       </c>
@@ -8176,7 +8239,7 @@
       <c r="AN98" s="303"/>
       <c r="AO98" s="304"/>
     </row>
-    <row r="99" spans="1:41" ht="20.25" customHeight="1">
+    <row r="99" spans="1:42" ht="20.25" customHeight="1">
       <c r="B99" s="285" t="s">
         <v>74</v>
       </c>
@@ -8186,7 +8249,7 @@
       <c r="F99" s="286"/>
       <c r="G99" s="286"/>
       <c r="H99" s="335" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I99" s="288"/>
       <c r="J99" s="288"/>
@@ -8222,7 +8285,7 @@
       <c r="AN99" s="288"/>
       <c r="AO99" s="289"/>
     </row>
-    <row r="100" spans="1:41" ht="20.25" customHeight="1">
+    <row r="100" spans="1:42" ht="20.25" customHeight="1">
       <c r="B100" s="290" t="s">
         <v>76</v>
       </c>
@@ -8232,7 +8295,7 @@
       <c r="F100" s="312"/>
       <c r="G100" s="312"/>
       <c r="H100" s="336" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I100" s="318"/>
       <c r="J100" s="318"/>
@@ -8268,10 +8331,10 @@
       <c r="AN100" s="318"/>
       <c r="AO100" s="319"/>
     </row>
-    <row r="101" spans="1:41" ht="19.5" customHeight="1">
+    <row r="101" spans="1:42" ht="19.5" customHeight="1">
       <c r="A101" s="55"/>
       <c r="B101" s="375" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C101" s="376"/>
       <c r="D101" s="376"/>
@@ -8325,7 +8388,7 @@
       <c r="AN101" s="369"/>
       <c r="AO101" s="370"/>
     </row>
-    <row r="102" spans="1:41" ht="9" customHeight="1">
+    <row r="102" spans="1:42" ht="9" customHeight="1">
       <c r="A102" s="104"/>
       <c r="B102" s="378"/>
       <c r="C102" s="376"/>
@@ -8374,7 +8437,7 @@
       <c r="AN102" s="372"/>
       <c r="AO102" s="373"/>
     </row>
-    <row r="103" spans="1:41" ht="20.25" customHeight="1" thickBot="1">
+    <row r="103" spans="1:42" ht="20.25" customHeight="1" thickBot="1">
       <c r="A103" s="104"/>
       <c r="B103" s="378"/>
       <c r="C103" s="376"/>
@@ -8382,47 +8445,62 @@
       <c r="E103" s="376"/>
       <c r="F103" s="376"/>
       <c r="G103" s="377"/>
-      <c r="H103" s="89"/>
+      <c r="H103" s="89" t="s">
+        <v>202</v>
+      </c>
       <c r="I103" s="90"/>
       <c r="J103" s="90"/>
       <c r="K103" s="99"/>
-      <c r="L103" s="101"/>
+      <c r="L103" s="101" t="s">
+        <v>201</v>
+      </c>
       <c r="M103" s="102"/>
       <c r="N103" s="102"/>
       <c r="O103" s="102"/>
       <c r="P103" s="103"/>
       <c r="Q103" s="19"/>
-      <c r="R103" s="101"/>
+      <c r="R103" s="101" t="s">
+        <v>206</v>
+      </c>
       <c r="S103" s="102"/>
       <c r="T103" s="102"/>
       <c r="U103" s="102"/>
       <c r="V103" s="103"/>
       <c r="W103" s="19"/>
-      <c r="X103" s="101"/>
+      <c r="X103" s="101" t="s">
+        <v>203</v>
+      </c>
       <c r="Y103" s="102"/>
       <c r="Z103" s="102"/>
       <c r="AA103" s="102"/>
       <c r="AB103" s="103"/>
-      <c r="AC103" s="19"/>
-      <c r="AD103" s="101"/>
+      <c r="AC103" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="AD103" s="101" t="s">
+        <v>204</v>
+      </c>
       <c r="AE103" s="102"/>
       <c r="AF103" s="102"/>
       <c r="AG103" s="102"/>
       <c r="AH103" s="102"/>
       <c r="AI103" s="374"/>
       <c r="AJ103" s="364" t="s">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="AK103" s="365"/>
       <c r="AL103" s="365"/>
       <c r="AM103" s="365"/>
       <c r="AN103" s="365"/>
       <c r="AO103" s="366"/>
-    </row>
-    <row r="104" spans="1:41" ht="15" customHeight="1" thickBot="1">
+      <c r="AP103" s="51" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:42" ht="15" customHeight="1" thickBot="1">
       <c r="A104" s="55"/>
       <c r="B104" s="105" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C104" s="106"/>
       <c r="D104" s="106"/>
@@ -8464,10 +8542,10 @@
       <c r="AN104" s="106"/>
       <c r="AO104" s="107"/>
     </row>
-    <row r="105" spans="1:41" ht="108" customHeight="1" thickBot="1">
+    <row r="105" spans="1:42" ht="108" customHeight="1" thickBot="1">
       <c r="A105" s="104"/>
       <c r="B105" s="357" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C105" s="358"/>
       <c r="D105" s="358"/>
